--- a/owlcms/src/main/resources/templates/teamResults/TeamResults-A4.xlsx
+++ b/owlcms/src/main/resources/templates/teamResults/TeamResults-A4.xlsx
@@ -1,68 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\teamResults\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C7288E-D150-458B-B389-C99852B7A07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="5280" windowWidth="30780" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Men" sheetId="1" r:id="rId1"/>
     <sheet name="Women" sheetId="2" r:id="rId2"/>
+    <sheet name="Mixed" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>owlcms</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>jx:area(lastCell="G6")</t>
+          <t>jx:area(lastCell="G7")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="A3" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>jx:each(items="mTeamItems" var="team" lastCell="G6")</t>
+          <t>jx:each(items="mTeamItems" var="team" lastCell="G7")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="A5" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>jx:each(items="team.sortedTeamMembers" var="member" lastCell="G5")</t>
         </r>
@@ -73,48 +65,94 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>owlcms</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>jx:area(lastCell="G6")</t>
+          <t>jx:area(lastCell="G7")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="A3" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>jx:each(items="wTeamItems" var="team" lastCell="G6")</t>
+          <t>jx:each(items="wTeamItems" var="team" lastCell="G7")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="A5" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
-            <scheme val="minor"/>
+          </rPr>
+          <t>jx:each(items="team.sortedTeamMembers" var="member" lastCell="G5")</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>owlcms</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>jx:area(lastCell="G7")</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>jx:each(items="mwTeamItems" var="team" lastCell="G7")</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
           </rPr>
           <t>jx:each(items="team.sortedTeamMembers" var="member" lastCell="G5")</t>
         </r>
@@ -125,30 +163,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="27">
   <si>
     <t>${competition.competitionName}</t>
   </si>
   <si>
-    <t>${championship != null ? championship.name : ""} ${ageGroupPrefix != null ? ageGroupPrefix : ""}</t>
-  </si>
-  <si>
-    <t>${t.get("Gender.M")}</t>
-  </si>
-  <si>
-    <t>${scoringTitle}</t>
+    <t>${championship != null ? championship.name : ""}</t>
+  </si>
+  <si>
+    <t>${ageGroupPrefix != null ? ageGroupPrefix : ""} ${t.get("Gender.M")}</t>
   </si>
   <si>
     <t>${team.name}</t>
   </si>
   <si>
-    <t>${team.points}</t>
-  </si>
-  <si>
-    <t>${team.counted} / ${team.size}</t>
-  </si>
-  <si>
-    <t>${team.score}</t>
+    <t>${mShowPoints &amp;&amp; team.points != 0 ? team.points : ""}</t>
+  </si>
+  <si>
+    <t>${team.counted}/${team.size}</t>
+  </si>
+  <si>
+    <t>${!mShowPoints &amp;&amp; team.score != 0 ? team.score : ""}</t>
   </si>
   <si>
     <t>#</t>
@@ -166,6 +201,9 @@
     <t>${t.get("Done")}</t>
   </si>
   <si>
+    <t>${mScoringTitle}</t>
+  </si>
+  <si>
     <t>${member.name}</t>
   </si>
   <si>
@@ -175,23 +213,47 @@
     <t>${member.category}</t>
   </si>
   <si>
-    <t>${member.points}</t>
+    <t>${member.points != null &amp;&amp; member.points != 0 ? member.points : ""}</t>
   </si>
   <si>
     <t>${member.done ? t.get("Done") : ""}</t>
   </si>
   <si>
-    <t>${member.score}</t>
-  </si>
-  <si>
-    <t>${t.get("Gender.F")}</t>
+    <t>${member.score != null &amp;&amp; member.score != 0 ? member.score : ""}</t>
+  </si>
+  <si>
+    <t>${ageGroupPrefix != null ? ageGroupPrefix : ""} ${t.get("Gender.F")}</t>
+  </si>
+  <si>
+    <t>${wShowPoints &amp;&amp; team.points != 0 ? team.points : ""}</t>
+  </si>
+  <si>
+    <t>${!wShowPoints &amp;&amp; team.score != 0 ? team.score : ""}</t>
+  </si>
+  <si>
+    <t>${wScoringTitle}</t>
+  </si>
+  <si>
+    <t>${ageGroupPrefix != null ? ageGroupPrefix : ""} ${t.get("Gender.MF")}</t>
+  </si>
+  <si>
+    <t>${mwShowPoints &amp;&amp; team.points != 0 ? team.points : ""}</t>
+  </si>
+  <si>
+    <t>${!mwShowPoints &amp;&amp; team.score != 0 ? team.score : ""}</t>
+  </si>
+  <si>
+    <t>${mwScoringTitle}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,16 +264,28 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -224,13 +298,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -261,27 +335,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -569,196 +647,289 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5" t="s">
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/owlcms/src/main/resources/templates/teamResults/TeamResults-A4.xlsx
+++ b/owlcms/src/main/resources/templates/teamResults/TeamResults-A4.xlsx
@@ -56,7 +56,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:each(items="team.sortedTeamMembers" var="member" lastCell="G5")</t>
+          <t>jx:each(items="team.countedTeamMembers" var="member" lastCell="G5")</t>
         </r>
       </text>
     </comment>
@@ -105,7 +105,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:each(items="team.sortedTeamMembers" var="member" lastCell="G5")</t>
+          <t>jx:each(items="team.countedTeamMembers" var="member" lastCell="G5")</t>
         </r>
       </text>
     </comment>
@@ -154,7 +154,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:each(items="team.sortedTeamMembers" var="member" lastCell="G5")</t>
+          <t>jx:each(items="team.countedTeamMembers" var="member" lastCell="G5")</t>
         </r>
       </text>
     </comment>
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
   <si>
     <t>${competition.competitionName}</t>
   </si>
@@ -180,7 +180,7 @@
     <t>${mShowPoints &amp;&amp; team.points != 0 ? team.points : ""}</t>
   </si>
   <si>
-    <t>${team.counted}/${team.size}</t>
+    <t>${team.counted}/${mTeamSize != 0 ? mTeamSize : team.size}</t>
   </si>
   <si>
     <t>${!mShowPoints &amp;&amp; team.score != 0 ? team.score : ""}</t>
@@ -228,6 +228,9 @@
     <t>${wShowPoints &amp;&amp; team.points != 0 ? team.points : ""}</t>
   </si>
   <si>
+    <t>${team.counted}/${wTeamSize != 0 ? wTeamSize : team.size}</t>
+  </si>
+  <si>
     <t>${!wShowPoints &amp;&amp; team.score != 0 ? team.score : ""}</t>
   </si>
   <si>
@@ -238,6 +241,9 @@
   </si>
   <si>
     <t>${mwShowPoints &amp;&amp; team.points != 0 ? team.points : ""}</t>
+  </si>
+  <si>
+    <t>${team.counted}/${mwTeamSize != 0 ? mwTeamSize : team.size}</t>
   </si>
   <si>
     <t>${!mwShowPoints &amp;&amp; team.score != 0 ? team.score : ""}</t>
@@ -783,10 +789,10 @@
         <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -807,7 +813,7 @@
         <v>11</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -865,7 +871,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -876,13 +882,13 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -903,7 +909,7 @@
         <v>11</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7">
